--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,8 +480,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,8 +507,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,8 +534,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,8 +561,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,8 +588,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -625,8 +615,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -641,7 +629,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>그래, 내 이름은…</t>
+          <t>그래, 내 이름은...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -654,7 +642,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>NameInput</t>
@@ -674,7 +661,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -687,8 +674,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -703,7 +688,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -716,8 +701,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -745,8 +728,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -774,8 +755,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -803,8 +782,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -832,8 +809,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -848,7 +823,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>그러면 답은 이미 정해졌다…</t>
+          <t>그러면 답은 이미 정해졌다...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -861,8 +836,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -890,8 +863,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -906,7 +877,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>생각보다…</t>
+          <t>생각보다...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -919,8 +890,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -948,8 +917,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -977,8 +944,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -993,7 +958,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>엇, 근데 집 밖에 나가려면 어떻게 해야 하더라…?</t>
+          <t>엇, 근데 집 밖에 나가려면 어떻게 해야 하더라...?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1006,8 +971,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1035,8 +998,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1064,8 +1025,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1093,8 +1052,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1122,8 +1079,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1151,8 +1106,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1180,8 +1133,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1209,8 +1160,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1238,8 +1187,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1267,8 +1214,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1296,8 +1241,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1325,8 +1268,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1354,8 +1295,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1383,8 +1322,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1412,8 +1349,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1428,16 +1363,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>좋습니다. 그럼 — 싸우자!</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>좋습니다. 그럼... 싸우자!</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>StartBattle</t>
@@ -1470,8 +1403,6 @@
           <t>stage1</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1489,14 +1420,11 @@
           <t>가출해 주겟슨~</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>stage1</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1506,22 +1434,1055 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>주인</t>
+          <t>{name}</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>집 비밀번호 강아지한테 다털렸쥬</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>아니 갑자기 공격하면 안 되지!</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>gp01</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stage1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gp01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>gp02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gp02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>공격은 그쪽이 먼저 했다고 생각합니다만?</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>gp03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gp03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>나는 괜찮은데 너는 안 돼!</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>gp04</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>gp04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>이것이 바로 내로남불이라고 하는 것인가요?</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>gp05</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gp05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>내가 하면 로망, 남이 하면 불장난!</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>gp06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gp06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>후후훗, 하지만 저는 로망도 불장난도 좋아하니 당신에게 나가는 법을 특별히 알려드리죠.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>gp07</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>gp07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>야! 어차피 내가 이겨서 알려줘야 하는 거잖아!</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>gp08</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>gp08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>멋을 모르다니 이래서 감 없는 꼬맹이는 싫다니까요?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>gp09</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gp09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>...!!!!!!!!!</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>gp10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gp10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>얼굴이 붉어졌군요.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>gp11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>gp11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>설마...</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>gp12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gp12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>화났나요?</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>gp13</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>gp13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>아니거든! 난 어른이라서 화 안 내거든?</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>gp14</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>gp14</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>어서 나가는 방법이나 말해줘!</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>gp15</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>gp15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>너랑 말하기 싫어!</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>gp16</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>gp16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>더 이상 놀리면 그 작은 입으로 나를 앙 물어버릴 것 같으니 알려드리죠!</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>gp17</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>gp17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>방금 나만큼 잘생기진 않았지만 꽤 나쁘지 않게 생긴 유령들이 가득했죠?</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>gp18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>gp18</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>털북숭이 그대가 이 방에서 나가고 싶으면 모든 유령을...</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>gp19</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gp19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>제거해야 합니다...!</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>gp20</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>gp20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>이런 무서워라! 지금 당장 도망치고 싶은걸요?</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>gp21</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gp21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>이제야 알았냐?!</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>gp22</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>gp22</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>후훗, 하지만 이 방에 꽤 많은 유령이 살고 있는 거 알고 있죠?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>gp23</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>gp23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>gp24</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>gp24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>...아니 몰랐는데?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>gp25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>gp25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>강아지 맞나? 어떻게 모르지?</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>gp26</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>gp26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>...! 아 잠시 컨셉이 흐트러졌군요!</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>gp27</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>gp27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>잊어버리세요!</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>gp28</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>gp28</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>근데 넌 날 왜 도와주는 거야?</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>gp29</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>gp29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>강아지를 제외한 모든 생명체는 이득 없이 움직이지 않는다구!</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>gp30</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>gp30</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>오! 지극히 강아지 중심적인 생각!</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>gp31</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>gp31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>그러나 대답해 주겠어요!</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>gp32</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>gp32</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>나는 이 방에 갇힌 지 올해로 17년째!</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>gp33</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>gp33</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>장난치고 사라질 생각으로 들어왔는데 결계가 쳐질 줄 몰랐죠!</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>gp34</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>gp34</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>믿기 힘들다고요? 그럼 저기 벽을 한번 봐 보세요!</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>gp35</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>InspectWall</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>gp35</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>...이거 뭐야 소름 돋아.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>gp36</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>gp36</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>후훗, 감동이죠?</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>gp37</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>gp37</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>이 방 주인이 뭔가 쎄하다고 뿌린 야매 성수가 원인인데...</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>gp38</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>gp38</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>말로 하면 길어요! 직접 보는 게 빠르겠군요!</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>InspectHolyWater</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1720,22 +2681,11 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>intro_stage1_pre</t>
@@ -1808,30 +2758,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>적이 조금 늘었다</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1884,30 +2820,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>점점 거세진다</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1960,30 +2882,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
           <t>쉽지 않아</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2036,30 +2944,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
           <t>거의 다 왔다</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2112,30 +3006,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
           <t>복도의 끝</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2188,24 +3068,11 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
           <t>복도를 지키는 무리</t>
@@ -2268,30 +3135,16 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>Reward_Stage1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
           <t>새로운 구역 골목이다</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,6 +509,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,6 +538,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -561,6 +567,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -615,6 +625,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -642,6 +654,7 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>NameInput</t>
@@ -674,6 +687,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -701,6 +716,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -728,6 +745,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,6 +774,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -782,6 +803,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -809,6 +832,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -836,6 +861,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,6 +890,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +919,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -917,6 +948,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -944,6 +977,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -971,6 +1006,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -998,6 +1035,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1025,6 +1064,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1052,6 +1093,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1079,6 +1122,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1106,6 +1151,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1133,6 +1180,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1160,6 +1209,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1187,6 +1238,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1214,6 +1267,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1241,6 +1296,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1268,6 +1325,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1295,6 +1354,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1322,6 +1383,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1349,6 +1412,8 @@
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1366,11 +1431,13 @@
           <t>좋습니다. 그럼... 싸우자!</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>chapter1</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>StartBattle</t>
@@ -1403,6 +1470,8 @@
           <t>stage1</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1420,11 +1489,14 @@
           <t>가출해 주겟슨~</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>stage1</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1452,6 +1524,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1479,6 +1553,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1506,6 +1582,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1533,6 +1611,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1560,6 +1640,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1587,6 +1669,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1614,6 +1698,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1641,6 +1727,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1668,6 +1756,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1695,6 +1785,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1722,6 +1814,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1749,6 +1843,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1776,6 +1872,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1803,6 +1901,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1830,6 +1930,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1857,6 +1959,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1884,6 +1988,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1911,6 +2017,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1938,6 +2046,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1965,6 +2075,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1992,6 +2104,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2019,6 +2133,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2046,6 +2162,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2073,6 +2191,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2100,6 +2220,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2127,6 +2249,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2154,6 +2278,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2181,6 +2307,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2208,6 +2336,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2235,6 +2365,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2262,6 +2394,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2289,6 +2423,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2316,6 +2452,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2343,6 +2481,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2370,6 +2510,7 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>InspectWall</t>
@@ -2402,6 +2543,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2429,6 +2572,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2456,6 +2601,8 @@
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2473,16 +2620,1352 @@
           <t>말로 하면 길어요! 직접 보는 게 빠르겠군요!</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>gp39</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>ghost1</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>InspectHolyWater</t>
         </is>
       </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>gp39</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>으윽...! 가까이만 해도 짜릿하군요!</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>gp40</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>gp40</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>이걸 정면으로 맞은 유령들이 초울트라슈퍼 유령으로 진화해 버렸다고요!</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>gp41</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>gp41</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>난 지금까지 유령 같은 거 못 봤는데?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>gp42</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>gp42</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>당신은 강아지가 아니라 돼지인가 보군요!</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>gp43</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>gp43</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>어쩐지!</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gp44</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>gp44</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>너 안 도와줄 거야!</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>gp45</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>gp45</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>후후, 그럴 수 없을 걸요?</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>gp46</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>gp46</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>나의 모습이 보이기 시작한 순간부터 당신도 저 초울트라크리처 유령들에게 영향을 받게 되었으니까요!</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>gp47</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>gp47</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>거짓말하지 마!</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>gp48</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>gp48</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>그럼 한번 시험해 볼까요? 저 문으로 가 보세요.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>gp49</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>gp49</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>(문에 다가가자 짜릿한 충격이 일었다.)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>gp50</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>gp50</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>짜릿짜릿하죠?</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>gp51</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>gp51</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>저거 뭔데!</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>gp52</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>gp52</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>진짜 뭔데!</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>gp53</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>gp53</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>저런 게 왜 우리 집에 있는 거야??</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>gp54</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>gp54</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>후훗, 서프라이즈!</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>gp55</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>gp55</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>서프라이즈는 개뿔! 어떻게 하면 저거 이길 수 있는 건데!?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>gp56</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>gp56</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>아까처럼 내가 처치하면 되는 거야?</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>gp57</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>gp57</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>아니죠, 아니죠. 지금의 당신은 너무 약해요!</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>gp58</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>gp58</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>!!!!!!!!</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>gp59</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>gp59</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>그</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>gp60</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>gp60</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>러</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>gp61</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>gp61</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>나</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>gp62</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>gp62</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>?!?!</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>gp63</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>gp63</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>당신은 방에 숨어있는 물건을 통해 강해질 수 있어요!</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>gp64</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>gp64</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>자, 당신의 휴식처 앞에 보이는 당근 인형이 보이죠? 잡아보세요!</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>gp65</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>gp65</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>(당근을 폴짝 잡았다.)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>gp66</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>gp66</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>잡혔죠? 당신의 주머니 안에 들어가 있을 겁니다!</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>gp67</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>gp67</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>자, 이제 당신의 안식처를 옆으로 살짝 치워봅시다!</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>gp68</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>gp68</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>(침대를 드래그해 옆으로 밀자 별 조각이 드러났다.)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>gp69</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>gp69</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>자, 이제 주머니를 자세히 봅시다! 그리고 그 둘을 합쳐보세요!</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>gp70</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>gp70</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>(인벤토리에서 당근과 별을 합치자 '떡내놔'가 등장했다.)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>gp71</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>gp71</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>당신은 강해졌습니다! 한 번 실험해 볼까요?</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>gp72</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>gp72</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>(스테이지 1-2로 향한다.)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>gp73</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>gp73</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>전보다 유령이 쉬워졌죠?</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>gp74</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>gp74</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>후후훗, 영업 비밀이지만 상황이 상황인지라 알려드립니다!</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>gp75</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>gp75</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>우리 108 귀신의 힘을 당신은 빌려 쓸 수 있어요!</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>gp76</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>gp76</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>헉!</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>gp77</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>gp77</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>이유를 알고 싶은가요?</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>gp78</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>gp78</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>(끄덕끄덕)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>gp79</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>gp79</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>그것은 당신이 강아지이기 때문입니다!</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>gp80</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>gp80</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>후훗 조합을 실패하면 약해지지만!</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>gp81</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>gp81</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>수많은 경우의 수가 존재하니 조합 실패하기를 실패하겠죠!</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>gp82</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>gp82</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>자! 싸우세요!</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>gp83</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>gp83</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>난 말을 너무 많이 해서 잠시 쉬고 있을게요!</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>gp84</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>gp84</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>유령</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>(크기가 축소되더니 점이 되어 사라진다.)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ghost1</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="dialogue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="stages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialogue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,8 +482,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,8 +509,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,8 +536,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,8 +563,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,8 +590,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -625,8 +617,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -654,7 +644,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>NameInput</t>
@@ -687,8 +676,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -716,8 +703,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -745,8 +730,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -774,8 +757,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -803,8 +784,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -832,8 +811,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -861,8 +838,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -890,8 +865,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -919,8 +892,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -948,8 +919,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -977,8 +946,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1006,8 +973,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1035,8 +1000,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1064,8 +1027,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1093,8 +1054,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1122,8 +1081,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1151,8 +1108,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1180,8 +1135,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1209,8 +1162,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1238,8 +1189,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1267,8 +1216,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1296,8 +1243,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1325,8 +1270,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1354,8 +1297,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1383,8 +1324,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1412,8 +1351,6 @@
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1431,13 +1368,11 @@
           <t>좋습니다. 그럼... 싸우자!</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>chapter1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>StartBattle</t>
@@ -1470,8 +1405,6 @@
           <t>stage1</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1489,14 +1422,11 @@
           <t>가출해 주겟슨~</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>stage1</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1524,8 +1454,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1553,8 +1481,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1582,8 +1508,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1611,8 +1535,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1640,8 +1562,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1669,8 +1589,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1698,8 +1616,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1727,8 +1643,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1756,8 +1670,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1785,8 +1697,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1814,8 +1724,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1843,8 +1751,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1872,8 +1778,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1901,8 +1805,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1930,8 +1832,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1959,8 +1859,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1988,8 +1886,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2017,8 +1913,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2046,8 +1940,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2075,8 +1967,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2104,8 +1994,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2133,8 +2021,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2162,8 +2048,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2191,8 +2075,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2220,8 +2102,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2249,8 +2129,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2278,8 +2156,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2307,8 +2183,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2336,8 +2210,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2365,8 +2237,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2394,8 +2264,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2423,8 +2291,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2452,8 +2318,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2481,8 +2345,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2510,7 +2372,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>InspectWall</t>
@@ -2543,8 +2404,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2572,8 +2431,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2601,8 +2458,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2630,7 +2485,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>InspectHolyWater</t>
@@ -2663,8 +2517,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2692,8 +2544,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2721,8 +2571,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2750,8 +2598,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2779,8 +2625,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2808,8 +2652,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2837,8 +2679,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2866,8 +2706,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2895,8 +2733,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2924,8 +2760,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2953,8 +2787,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2982,8 +2814,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3011,8 +2841,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3040,8 +2868,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3069,8 +2895,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3098,8 +2922,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3127,8 +2949,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3156,8 +2976,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3185,8 +3003,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3214,8 +3030,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3243,8 +3057,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3272,8 +3084,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3301,8 +3111,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3330,8 +3138,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3359,8 +3165,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3388,8 +3192,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3417,8 +3219,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3446,8 +3246,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3475,8 +3273,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3504,8 +3300,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3533,8 +3327,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3562,8 +3354,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3591,8 +3381,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3620,8 +3408,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3649,8 +3435,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3678,8 +3462,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3707,8 +3489,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3736,8 +3516,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3765,8 +3543,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3794,8 +3570,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3823,8 +3597,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3852,8 +3624,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3881,8 +3651,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3910,8 +3678,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3939,8 +3705,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3958,14 +3722,11 @@
           <t>(크기가 축소되더니 점이 되어 사라진다.)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>ghost1</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4632,4 +4393,3995 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>displayName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>별</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>각 맵에 랜덤으로 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>holyWater</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>성수병</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>주인의 방 (침대 아래)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>heart</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>하트</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>각 맵에 랜덤으로 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mismatchedSocks</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>짝짝이 양말</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>바닥</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>smellySocks</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>냄새나는 양말</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>침대 아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>matchingSocks</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>짝짝이 잘 맞는 양말</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>방</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>바닥</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rustyKey</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>녹슨 열쇠</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>현관</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>현관 선반 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tornUmbrella</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>찢어진 우산</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>현관</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>우산꽂이</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>parcelBox</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>택배상자</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>현관</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>현관 바닥</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fryingPan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>프라이팬</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>주방</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>싱크대 걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>expiredMilk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>주방</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>냉장고 안쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>wasabi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>고추냉이</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>주방</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>냉장고 구석</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ladle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>국자</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>주방</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>서랍 안</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>foil</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>쿠킹호일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>주방</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>조리대 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>당근인형</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>침대 앞</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>threeKingdoms</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>삼국지 책</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>책상 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>teddyBear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>곰인형</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>침대 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>리모컨</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>이불 속</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brokenMirror</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>깨진 거울</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>화장대 밑</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>needleThread</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>실과 바늘</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>서랍 안</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sunglasses</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>썬글라스</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>책상 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>witheredFlower</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>시든꽃</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>주인의 방</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>창가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>broom</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>빗자루</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>거실</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>구석</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cushion</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>쿠션</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>거실</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>소파 밑</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dustBunny</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>먼지뭉치</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>거실</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TV 뒤</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>chargerCable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>충전기 줄</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>거실</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>소파 틈</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>건전지</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>거실</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>서랍 안</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bamboo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>대나무</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>마당</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>울타리 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>돌멩이</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>마당</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>화단 옆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dandelion</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>민들레</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>마당</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>잔디밭</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>earthworm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>지렁이</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>마당</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>흙 속</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hose</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>호스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>마당</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>수도꼭지 연결</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>resultName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>resultEn</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ingredients</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>똥개</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mutt</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>성능 구림 (조합 실패 시 무조건 등장), 공격력 -10%, 속도 -10%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>조합 실패 시 fallback / 적 아이템아이템 드랍률 +15%, 공격 수동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>적토견</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RedHareDog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>당근인형;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>시야가 가려지는 대신 공격력 대폭 상승(50%)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>바니견</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BunnyDog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>당근인형;별</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>속도가 빨라진다(30%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-1장수돌침대</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>StoneBed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>별;별;별;별</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>별을 쏘기 시작한다(공격력 40%상승, 방어력 40% 상승)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>견법소년</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KungFuDogBoy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>별;성수병;하트</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3초에 한 번씩 강한 공격을 한다</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>개죽이</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SmilingPup</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>대나무</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>치명적인 미소로 원하는 순간 적을 3초간 멈추게 만든다</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>패셔니스타견</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FashionistaDog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>짝짝이 양말</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>공격 속도가 1.5배 빨라진다</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>루광견</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LupinDog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>녹슨 열쇠</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>적 처치 시 아이템 드롭 확률 상승</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>낭만견</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RomanticDog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>찢어진 우산;실과 바늘</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>적과 충돌 시 2번 완전 방어된다</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>서프라이즈!</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>택배상자</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3초간 상자에서 무차별 공격이 발사된다 (쿨타임 12초)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>취두부견</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>StinkyTofuDog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>냄새나는 양말;찢어진 우산</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>이동 경로에 악취 웅덩이 생성, 밟은 적 지속 데미지</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>산타견</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SantaDog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>짝짝이 양말;택배상자</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>랜덤 위치에 폭발 상자 3개 투하</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>별을 헤매는 견</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>StargazerDog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>녹슨 열쇠;별</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>하늘에서 별인형이 떨어진다. 충돌 시 적 즉사</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>판도라 택배</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PandoraParcel</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>녹슨 열쇠;택배상자</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>상자 열면 랜덤 효과 (강화/회복 중 하나) (쿨타임 15초)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>돌진견</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ChargeDog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>찢어진 우산;택배상자</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>전방에서 오는 원거리 공격 3회 반사, 공격한 적의 HP 감소</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>싸패견</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PsychoDog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>짝짝이 잘 맞는 양말;썬글라스</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>공격력이 10% 증가</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>수상한 외출</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SneakyOuting</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>짝짝이 양말;시든꽃;찢어진 우산</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10초간 이속 대폭 상승 + 접촉한 적 밀어내기 + 공격력 3% 증가</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>보물</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>짝짝이 양말;녹슨 열쇠;택배상자</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>보물을 지키기 위해 공격력이 5% 증가한다</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>우편배달부</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mailman</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>찢어진 우산;택배상자;녹슨 열쇠</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>지정한 적에게 폭발 택배를 정확히 배달, -50% 데미지</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1회 사용 후 일반 강아지로</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>만리장성견</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GreatWallDog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>짝짝이 양말;녹슨 열쇠;찢어진 우산;택배상자</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5초간 바리케이드 생성, 적 충돌 시 데미지 30% 감소</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1회 사용 후 일반 강아지로</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>후라이깡</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PanWhack</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>프라이팬</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>근접 타격, 적과 특정 거리 도달 시 근접 공격 -40% 데미지</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>이런우유는싫어요</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MilkHater</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>랜덤으로 우유 폭탄 발사, 적 이동속도 15% 감소</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>작은 고추가 강하다</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MightyPepper</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>고추냉이</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>전방 부채꼴 매운 안개, 적 공격력 대폭 감소</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>퍼담아!</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ScoopBack</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>국자</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>적의 투사체를 쳐서 되돌림, 맞출시 데미지 150% 증가</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>은박갑옷</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FoilArmor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>쿠킹호일</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5초간 받는 데미지 50% 감소</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>독요리사</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PoisonChef</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>프라이팬;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>타격한 적이 5초간 동료 적을 공격함 (혼란)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>화염팬</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FlamePan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>프라이팬;고추냉이</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>근접 타격이 화상 부여, 3초간 지속 데미지</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>생화학무기</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Biohazard</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>고추냉이;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>자기 주변 넓은 범위 지속 데미지 장판 8초</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>위성안테나</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SatelliteDish</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>국자;쿠킹호일</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10초간 적 전원 위치 표시 + 가장 먼 적에게 자동 공격</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>타악기견</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PercussionDog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>프라이팬;국자</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3초간 주변에 리듬 충격파, 박자마다 적 넉백</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>매운은박구이</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SpicyFoilGrill</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>쿠킹호일;고추냉이</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>설치형 함정, 밟은 적 즉시 경직 + 방어력 감소</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>자물쇠깨기</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LockBreaker</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>프라이팬;녹슨 열쇠</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>보스 방어막 무시하고 직접 타격 가능 (10초)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>역대급악취</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UltimateStench</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>유통기한 지난 우유;짝짝이 양말</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>맵 전체 적 이동속도 30% 감소 15초간</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>매운비</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SpicyRain</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>고추냉이;찢어진 우산</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>하늘에서 고추냉이 비가 내림, 전체 적 지속 데미지 3초(-10%), 쿨타임 20초</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>출장요리사</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CateringChef</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>택배상자;프라이팬</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>랜덤 위치 3곳에 프라이팬 내려찍기, 범위 스턴</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>은박택배</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FoilParcel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>쿠킹호일;택배상자</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>적에게 달라붙는 시한폭탄 부착, 3초 후 폭발</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>바람국자</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WindLadle</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>국자;찢어진 우산</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>전방에 강한 바람, 적 전원 위쪽으로 밀어내기</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>적벽대전</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RedCliffsBattle</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>프라이팬;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>전방 넓은 부채꼴 화염 공격, 적 전원 화상(지속 대미지 -5%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>매운토끼</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SpicyRabbit</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>당근인형;고추냉이</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>당근 유도탄 3발 발사, 맞은 적 경직 + 지속 데미지</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>배탈곰</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UpsetTummyBear</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>곰인형;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>자폭형 곰인형 소환, 적에게 걸어가서 폭발</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>홈쇼핑</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HomeShopping</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>리모컨;프라이팬</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5초간 공격속도 2배</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>거울나라의 국자</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MirrorLandLadle</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>깨진 거울;국자</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>자신의 공격이 전부 2회 반복됨 (8초간)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>전파교란</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SignalJam</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>리모컨;쿠킹호일</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>적 전원 3초간 랜덤 방향으로 이동 (조작 반전)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>지옥의주방</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HellsKitchen</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>프라이팬;고추냉이;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>맵 전체 10초간 모든 적 지속 데미지 + 혼란</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>테러인형</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TerrorDoll</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>짝짝이 양말;고추냉이;곰인형</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>곰인형이 적진 돌진, 범위 기절 + 중독</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>군영취사병</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ArmyCook</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>삼국지 책;국자;프라이팬;녹슨 열쇠</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20초간 아군 유닛 3마리 소환</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UFO견</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UfoDog</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>쿠킹호일;깨진 거울;리모컨</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>쿠킹호일 UFO 오라, 5초간 적 공격 무시 + 자동 레이저 공격</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>생존키트</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SurvivalKit</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>택배상자;유통기한 지난 우유;찢어진 우산;쿠킹호일</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1회 부활 + 부활 시 주변 적 밀어내기 + 3초 무적</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>당근방패</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CarrotShield</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>당근인형</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>피격 시 당근 파편이 주변 적에게 반사 데미지</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>포근방패</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CozyShield</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>곰인형</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>피격 시 30% 확률로 데미지 무효화</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>일시정지</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pause</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>리모컨</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>화면 내 적 전체 1.5초 정지 (쿨타임 10초)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>지략견</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>StrategistDog</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>삼국지 책</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>적이 서로 가장 가까운 적을 공격함 (동요 5초)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>저주인형</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CurseDoll</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>곰인형;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>받은 데미지 200%를 가장 가까운 적에게 전달 (8초)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>채널서핑</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ChannelSurf</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>리모컨;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5초마다 랜덤 버프 1개 부여 (20초간)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>채널돌리개</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ChannelShuffle</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>리모컨;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>적들의 위치를 랜덤으로 섞어버림</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>인형극단</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PuppetTroupe</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>곰인형;당근인형</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>인형 2개가 주변을 돌며 자동 공격</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>관곰</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BearGuanYu</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>곰인형;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>15초간 공격력 대폭 상승 + 타격 시 적 밀어내기</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>당근미사일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CarrotMissile</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>리모컨;당근인형</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>리모컨 누르면 유도 당근 5발 연속 발사</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>동탁의거울</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DongtakMirror</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>깨진 거울;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>가장 강한 적 1마리 10초간 아군 전환,</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>한 번 사용 시 15초가 끝나면 일반 개로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>인형군단</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DollLegion</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>당근인형;곰인형;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>분신 인형 5개 소환, 각각 자동 공격 10초</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>삼국지극장</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ThreeKingdomsShow</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>리모컨;삼국지 책;깨진 거울;곰인형</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>관우·장비·조조 곰인형 3마리 소환, 15초간 전투</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>한 번 사용 시 15초가 끝나면 일반 개로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>쓸어버려!</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SweepAway</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>빗자루</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>근접공격, 전방 넓은 범위 밀어내기 공격</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>쿠션범퍼</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CushionBumper</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>쿠션</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>적과 충돌 시 자동 넉백 + 충격파 데미지</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>먼지구름</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DustCloud</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>먼지뭉치</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>5초간 회피율 80%, 적 공격이 거의 안 맞음</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>채찍개</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>WhipDog</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>충전기 줄</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>사거리 2배 증가, 긴 거리에서 적 타격 가능</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>에너자이개</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EnergizerDog</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>건전지</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>10초간 모든 쿨타임 50% 감소</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>먼지폭풍</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DustStorm</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>빗자루;먼지뭉치</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>토네이도 소환, 적을 빨아들여 한곳에 모은 뒤 폭발</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>전기견</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ElectricDog</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>충전기 줄;건전지</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>공격마다 감전, 감전된 적끼리 가까우면 연쇄 번개</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>마녀견</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>WitchDog</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>쿠션;빗자루</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10초간 적 공격 무시 + 위에서 쿠션 투하 공격</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>알레르기폭탄</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AllergyBomb</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>쿠션;먼지뭉치</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>적 전원 재채기, 3초간 공격 불가</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>전기빗자루</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ElectricBroom</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>충전기 줄;빗자루</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>전방 쓸기 공격에 감전 추가, 감전시 4초간 정지, 데미지 40% 감소</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>전기방석</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ElectricCushion</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>건전지;쿠션</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>터치로 원하는 곳에 설치, 밟은 적 5초간 감전으로 이동불가, 쿨타임 5초, 한 번 밟으면 사라짐</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>완전체리모컨</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UltimateRemote</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>건전지;리모컨</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>적 1마리 지정, 가장 가까이에 있는 적에게 돌진하여 동귀어진</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>정전기개</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>StaticDog</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>충전기 줄;짝짝이 양말</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>접촉한 적 전원 3초 마비, 연쇄 감전</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>곰팡이포자</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MoldSpore</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>먼지뭉치;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>맵에 곰팡이 지대 생성, 적 지속 데미지 + 둔화</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>당근펀치</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CarrotPunch</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>빗자루;당근인형</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>이동속도 상승 + 당근 인형이 10초에 한 번씩 갈림, 당근 인형을 밟으면 속도 50% 감소</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>낮잠세트</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NapSet</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>쿠션;곰인형</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>주변 적 전원 수면 5초, 피격 시 깨어남</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>레이저견</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LaserDog</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>건전지;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>거울에서 레이저 반사, 직선상 적 전원 관통 데미지</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>전기요리사</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ElectricChef</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>충전기 줄;국자;프라이팬</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>감전 프라이팬 3연타 + 마지막 타격 범위 폭발</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>쓰레기폭풍</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TrashStorm</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>먼지뭉치;택배상자;찢어진 우산</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>잡동사니 토네이도, 적 끌어모아 12초간 지속 데미지</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>대마법사견</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ArchmageDog</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>빗자루;녹슨 열쇠;깨진 거울;건전지</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>10초간 적 공격 무시 + 번개 자동 공격 + 분신 소환</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>돌머리</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>StoneHead</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>돌멩이</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>방어력 대폭 상승, 이동속도 30% 감소</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>민들레솜</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DandelionFluff</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>민들레</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>8초간 적 공격 무시 + 홀씨 자동 범위 공격</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>땅굴개</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TunnelDog</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>지렁이</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>지하 잠입, 3초 후 지정 위치에서 솟아올라 범위 공격</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>워터건</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>WaterGun</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>호스</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>전방 직선 물줄기, 적 밀어내기 + 3초 둔화</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>석궁견</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CrossbowDog</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>대나무;돌멩이</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>돌멩이를 대나무로 발사, 관통형 원거리 공격</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>꽃비</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FlowerRain</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>호스;민들레</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>홀씨가 맵 전체 흩뿌려짐, 적 전원 시야 차단 5초</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>지진개</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EarthquakeDog</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>지렁이;돌멩이</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>땅을 흔들어 맵 전체 적 넘어뜨림 2초</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>진흙탕</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Mudpit</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>호스;지렁이</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>맵 바닥 진흙 변경, 적 이동속도 50% 감소 10초</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>대나무피리</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BambooFlute</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>대나무;민들레</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>아름다운 선율, 적 전원 매혹 5초간 제자리 춤</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>물대포</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>WaterCannon</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>대나무;호스</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>대나무 통에 물 압축, 전방 초강력 일직선 공격</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>돌구이</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>StoneGrill</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>돌멩이;프라이팬</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>달궈진 돌 투척 3발, 맞은 자리에 화상 장판</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>감전호스</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ShockHose</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>호스;충전기 줄;건전지</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>물줄기에 전기, 맞은 적 전원 연쇄 감전</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>낚시개</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FishingDog</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>지렁이;곰인형</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>지렁이 미끼로 적 끌어당겨 곰인형이 5초 속박</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>환상의꽃</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IllusionFlower</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>민들레;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>분신 3마리 각각 민들레 홀씨 공격, 넓은 범위</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>제갈량견</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ZhugeLiangDog</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>대나무;삼국지 책</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>15초간 적 이동 경로 예측 + 함정 자동 설치</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>투석기</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Catapult</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>돌멩이;쿠션</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>쿠션에 돌 올려 발사, 포물선 범위 공격 3연발</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>상한분수</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SpoiledFountain</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>호스;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>독우유 분수 뿌림, 주변 적 중독 + 둔화</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>아웃사이더</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Outsider</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>지렁이;먼지뭉치;짝짝이 양말</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>너무 역겨워서 적 전원 도망 8초</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>꽃바람청소</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FlowerWindSweep</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>민들레;빗자루</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>홀씨 토네이도, 적 빨아들인 뒤 큰 데미지</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>전기봉</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ElectricRod</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>대나무;충전기 줄</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>근접 공격 시 100% 감전 + 범위 확대</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>골렘소환</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GolemSummon</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>돌멩이;녹슨 열쇠;깨진 거울</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>돌 골렘 1마리 소환, 20초간 대신 싸워줌</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>최루가스</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TearGas</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>호스;고추냉이;민들레</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>맵 전체 안개, 적 명중률 0%에 가까움 3초</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>인형조종술</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PuppetControl</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>대나무;당근인형;리모컨</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>거대 당근인형 소환, 리모컨으로 직접 조종 12초</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>마녀의수프</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>WitchsSoup</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>지렁이;국자;유통기한 지난 우유</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>독 가마솥 설치, 주변 적 흡입 + 데미지</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>성벽건설</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>WallBuild</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>돌멩이;돌멩이;대나무;호스</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>맵에 돌벽 3개 생성, 적 부딪히면 데미지</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>정원의주인</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GardenMaster</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>대나무;돌멩이;민들레;지렁이</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>마당 전체 아군 영역, 적 자동 데미지 + 아군 회복 20초</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>한물간스타</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FadedStar</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>썬글라스;시든꽃;냄새나는 양말</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>적 전원 비웃음, 5초간 방어력 0으로 감소</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stages" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="characters" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5357,7 +5358,6 @@
           <t>Mutt</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>성능 구림 (조합 실패 시 무조건 등장), 공격력 -10%, 속도 -10%</t>
@@ -5395,7 +5395,6 @@
           <t>시야가 가려지는 대신 공격력 대폭 상승(50%)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5423,7 +5422,6 @@
           <t>속도가 빨라진다(30%)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5451,7 +5449,6 @@
           <t>별을 쏘기 시작한다(공격력 40%상승, 방어력 40% 상승)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5479,7 +5476,6 @@
           <t>3초에 한 번씩 강한 공격을 한다</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5507,7 +5503,6 @@
           <t>치명적인 미소로 원하는 순간 적을 3초간 멈추게 만든다</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5535,7 +5530,6 @@
           <t>공격 속도가 1.5배 빨라진다</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5563,7 +5557,6 @@
           <t>적 처치 시 아이템 드롭 확률 상승</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5591,7 +5584,6 @@
           <t>적과 충돌 시 2번 완전 방어된다</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5619,7 +5611,6 @@
           <t>3초간 상자에서 무차별 공격이 발사된다 (쿨타임 12초)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5647,7 +5638,6 @@
           <t>이동 경로에 악취 웅덩이 생성, 밟은 적 지속 데미지</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5675,7 +5665,6 @@
           <t>랜덤 위치에 폭발 상자 3개 투하</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5703,7 +5692,6 @@
           <t>하늘에서 별인형이 떨어진다. 충돌 시 적 즉사</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5731,7 +5719,6 @@
           <t>상자 열면 랜덤 효과 (강화/회복 중 하나) (쿨타임 15초)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5759,7 +5746,6 @@
           <t>전방에서 오는 원거리 공격 3회 반사, 공격한 적의 HP 감소</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5787,7 +5773,6 @@
           <t>공격력이 10% 증가</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5815,7 +5800,6 @@
           <t>10초간 이속 대폭 상승 + 접촉한 적 밀어내기 + 공격력 3% 증가</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5843,7 +5827,6 @@
           <t>보물을 지키기 위해 공격력이 5% 증가한다</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5935,7 +5918,6 @@
           <t>근접 타격, 적과 특정 거리 도달 시 근접 공격 -40% 데미지</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5963,7 +5945,6 @@
           <t>랜덤으로 우유 폭탄 발사, 적 이동속도 15% 감소</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5991,7 +5972,6 @@
           <t>전방 부채꼴 매운 안개, 적 공격력 대폭 감소</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6019,7 +5999,6 @@
           <t>적의 투사체를 쳐서 되돌림, 맞출시 데미지 150% 증가</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6047,7 +6026,6 @@
           <t>5초간 받는 데미지 50% 감소</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6075,7 +6053,6 @@
           <t>타격한 적이 5초간 동료 적을 공격함 (혼란)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6103,7 +6080,6 @@
           <t>근접 타격이 화상 부여, 3초간 지속 데미지</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6131,7 +6107,6 @@
           <t>자기 주변 넓은 범위 지속 데미지 장판 8초</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6159,7 +6134,6 @@
           <t>10초간 적 전원 위치 표시 + 가장 먼 적에게 자동 공격</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6187,7 +6161,6 @@
           <t>3초간 주변에 리듬 충격파, 박자마다 적 넉백</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6215,7 +6188,6 @@
           <t>설치형 함정, 밟은 적 즉시 경직 + 방어력 감소</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6243,7 +6215,6 @@
           <t>보스 방어막 무시하고 직접 타격 가능 (10초)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6271,7 +6242,6 @@
           <t>맵 전체 적 이동속도 30% 감소 15초간</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6299,7 +6269,6 @@
           <t>하늘에서 고추냉이 비가 내림, 전체 적 지속 데미지 3초(-10%), 쿨타임 20초</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6327,7 +6296,6 @@
           <t>랜덤 위치 3곳에 프라이팬 내려찍기, 범위 스턴</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6355,7 +6323,6 @@
           <t>적에게 달라붙는 시한폭탄 부착, 3초 후 폭발</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6383,7 +6350,6 @@
           <t>전방에 강한 바람, 적 전원 위쪽으로 밀어내기</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6411,7 +6377,6 @@
           <t>전방 넓은 부채꼴 화염 공격, 적 전원 화상(지속 대미지 -5%)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6439,7 +6404,6 @@
           <t>당근 유도탄 3발 발사, 맞은 적 경직 + 지속 데미지</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6467,7 +6431,6 @@
           <t>자폭형 곰인형 소환, 적에게 걸어가서 폭발</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6495,7 +6458,6 @@
           <t>5초간 공격속도 2배</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6523,7 +6485,6 @@
           <t>자신의 공격이 전부 2회 반복됨 (8초간)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6551,7 +6512,6 @@
           <t>적 전원 3초간 랜덤 방향으로 이동 (조작 반전)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6579,7 +6539,6 @@
           <t>맵 전체 10초간 모든 적 지속 데미지 + 혼란</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6607,7 +6566,6 @@
           <t>곰인형이 적진 돌진, 범위 기절 + 중독</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6635,7 +6593,6 @@
           <t>20초간 아군 유닛 3마리 소환</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6663,7 +6620,6 @@
           <t>쿠킹호일 UFO 오라, 5초간 적 공격 무시 + 자동 레이저 공격</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6691,7 +6647,6 @@
           <t>1회 부활 + 부활 시 주변 적 밀어내기 + 3초 무적</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6719,7 +6674,6 @@
           <t>피격 시 당근 파편이 주변 적에게 반사 데미지</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6747,7 +6701,6 @@
           <t>피격 시 30% 확률로 데미지 무효화</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6775,7 +6728,6 @@
           <t>화면 내 적 전체 1.5초 정지 (쿨타임 10초)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6803,7 +6755,6 @@
           <t>적이 서로 가장 가까운 적을 공격함 (동요 5초)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6831,7 +6782,6 @@
           <t>받은 데미지 200%를 가장 가까운 적에게 전달 (8초)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6859,7 +6809,6 @@
           <t>5초마다 랜덤 버프 1개 부여 (20초간)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6887,7 +6836,6 @@
           <t>적들의 위치를 랜덤으로 섞어버림</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6915,7 +6863,6 @@
           <t>인형 2개가 주변을 돌며 자동 공격</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6943,7 +6890,6 @@
           <t>15초간 공격력 대폭 상승 + 타격 시 적 밀어내기</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6971,7 +6917,6 @@
           <t>리모컨 누르면 유도 당근 5발 연속 발사</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7031,7 +6976,6 @@
           <t>분신 인형 5개 소환, 각각 자동 공격 10초</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7091,7 +7035,6 @@
           <t>근접공격, 전방 넓은 범위 밀어내기 공격</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7119,7 +7062,6 @@
           <t>적과 충돌 시 자동 넉백 + 충격파 데미지</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7147,7 +7089,6 @@
           <t>5초간 회피율 80%, 적 공격이 거의 안 맞음</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7175,7 +7116,6 @@
           <t>사거리 2배 증가, 긴 거리에서 적 타격 가능</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7203,7 +7143,6 @@
           <t>10초간 모든 쿨타임 50% 감소</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7231,7 +7170,6 @@
           <t>토네이도 소환, 적을 빨아들여 한곳에 모은 뒤 폭발</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7259,7 +7197,6 @@
           <t>공격마다 감전, 감전된 적끼리 가까우면 연쇄 번개</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7287,7 +7224,6 @@
           <t>10초간 적 공격 무시 + 위에서 쿠션 투하 공격</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7315,7 +7251,6 @@
           <t>적 전원 재채기, 3초간 공격 불가</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7343,7 +7278,6 @@
           <t>전방 쓸기 공격에 감전 추가, 감전시 4초간 정지, 데미지 40% 감소</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7371,7 +7305,6 @@
           <t>터치로 원하는 곳에 설치, 밟은 적 5초간 감전으로 이동불가, 쿨타임 5초, 한 번 밟으면 사라짐</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7399,7 +7332,6 @@
           <t>적 1마리 지정, 가장 가까이에 있는 적에게 돌진하여 동귀어진</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7427,7 +7359,6 @@
           <t>접촉한 적 전원 3초 마비, 연쇄 감전</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7455,7 +7386,6 @@
           <t>맵에 곰팡이 지대 생성, 적 지속 데미지 + 둔화</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7483,7 +7413,6 @@
           <t>이동속도 상승 + 당근 인형이 10초에 한 번씩 갈림, 당근 인형을 밟으면 속도 50% 감소</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7511,7 +7440,6 @@
           <t>주변 적 전원 수면 5초, 피격 시 깨어남</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7539,7 +7467,6 @@
           <t>거울에서 레이저 반사, 직선상 적 전원 관통 데미지</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7567,7 +7494,6 @@
           <t>감전 프라이팬 3연타 + 마지막 타격 범위 폭발</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7595,7 +7521,6 @@
           <t>잡동사니 토네이도, 적 끌어모아 12초간 지속 데미지</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7623,7 +7548,6 @@
           <t>10초간 적 공격 무시 + 번개 자동 공격 + 분신 소환</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7651,7 +7575,6 @@
           <t>방어력 대폭 상승, 이동속도 30% 감소</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7679,7 +7602,6 @@
           <t>8초간 적 공격 무시 + 홀씨 자동 범위 공격</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7707,7 +7629,6 @@
           <t>지하 잠입, 3초 후 지정 위치에서 솟아올라 범위 공격</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7735,7 +7656,6 @@
           <t>전방 직선 물줄기, 적 밀어내기 + 3초 둔화</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7763,7 +7683,6 @@
           <t>돌멩이를 대나무로 발사, 관통형 원거리 공격</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7791,7 +7710,6 @@
           <t>홀씨가 맵 전체 흩뿌려짐, 적 전원 시야 차단 5초</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7819,7 +7737,6 @@
           <t>땅을 흔들어 맵 전체 적 넘어뜨림 2초</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7847,7 +7764,6 @@
           <t>맵 바닥 진흙 변경, 적 이동속도 50% 감소 10초</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7875,7 +7791,6 @@
           <t>아름다운 선율, 적 전원 매혹 5초간 제자리 춤</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7903,7 +7818,6 @@
           <t>대나무 통에 물 압축, 전방 초강력 일직선 공격</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7931,7 +7845,6 @@
           <t>달궈진 돌 투척 3발, 맞은 자리에 화상 장판</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7959,7 +7872,6 @@
           <t>물줄기에 전기, 맞은 적 전원 연쇄 감전</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7987,7 +7899,6 @@
           <t>지렁이 미끼로 적 끌어당겨 곰인형이 5초 속박</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8015,7 +7926,6 @@
           <t>분신 3마리 각각 민들레 홀씨 공격, 넓은 범위</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8043,7 +7953,6 @@
           <t>15초간 적 이동 경로 예측 + 함정 자동 설치</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8071,7 +7980,6 @@
           <t>쿠션에 돌 올려 발사, 포물선 범위 공격 3연발</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8099,7 +8007,6 @@
           <t>독우유 분수 뿌림, 주변 적 중독 + 둔화</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8127,7 +8034,6 @@
           <t>너무 역겨워서 적 전원 도망 8초</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8155,7 +8061,6 @@
           <t>홀씨 토네이도, 적 빨아들인 뒤 큰 데미지</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8183,7 +8088,6 @@
           <t>근접 공격 시 100% 감전 + 범위 확대</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8211,7 +8115,6 @@
           <t>돌 골렘 1마리 소환, 20초간 대신 싸워줌</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8239,7 +8142,6 @@
           <t>맵 전체 안개, 적 명중률 0%에 가까움 3초</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8267,7 +8169,6 @@
           <t>거대 당근인형 소환, 리모컨으로 직접 조종 12초</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8295,7 +8196,6 @@
           <t>독 가마솥 설치, 주변 적 흡입 + 데미지</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8323,7 +8223,6 @@
           <t>맵에 돌벽 3개 생성, 적 부딪히면 데미지</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8351,7 +8250,6 @@
           <t>마당 전체 아군 영역, 적 자동 데미지 + 아군 회복 20초</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8379,7 +8277,1856 @@
           <t>적 전원 비웃음, 5초간 방어력 0으로 감소</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>displayName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mutt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>똥개</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>성능 구림 (조합 실패 시 무조건 등장), 공격력 -10%, 속도 -10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BunnyDog</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>바니견</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>속도가 빨라진다(30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>StoneBed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-1장수돌침대</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>별을 쏘기 시작한다(공격력 40%상승, 방어력 40% 상승)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KungFuDogBoy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>견법소년</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3초에 한 번씩 강한 공격을 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SmilingPup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>개죽이</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>치명적인 미소로 원하는 순간 적을 3초간 멈추게 만든다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FashionistaDog</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>패셔니스타견</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>공격 속도가 1.5배 빨라진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LupinDog</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>루광견</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>적 처치 시 아이템 드롭 확률 상승</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RomanticDog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>낭만견</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>적과 충돌 시 2번 완전 방어된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>서프라이즈!</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3초간 상자에서 무차별 공격이 발사된다 (쿨타임 12초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>StinkyTofuDog</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>취두부견</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>이동 경로에 악취 웅덩이 생성, 밟은 적 지속 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SantaDog</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>산타견</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>랜덤 위치에 폭발 상자 3개 투하</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>StargazerDog</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>별을 헤매는 견</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>하늘에서 별인형이 떨어진다. 충돌 시 적 즉사</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PandoraParcel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>판도라 택배</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>상자 열면 랜덤 효과 (강화/회복 중 하나) (쿨타임 15초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ChargeDog</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>돌진견</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>전방에서 오는 원거리 공격 3회 반사, 공격한 적의 HP 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PsychoDog</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>싸패견</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>공격력이 10% 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SneakyOuting</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>수상한 외출</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10초간 이속 대폭 상승 + 접촉한 적 밀어내기 + 공격력 3% 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>보물</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>보물을 지키기 위해 공격력이 5% 증가한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mailman</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>우편배달부</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>지정한 적에게 폭발 택배를 정확히 배달, -50% 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GreatWallDog</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>만리장성견</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5초간 바리케이드 생성, 적 충돌 시 데미지 30% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PanWhack</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>후라이깡</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>근접 타격, 적과 특정 거리 도달 시 근접 공격 -40% 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MilkHater</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>이런우유는싫어요</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>랜덤으로 우유 폭탄 발사, 적 이동속도 15% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MightyPepper</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>작은 고추가 강하다</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>전방 부채꼴 매운 안개, 적 공격력 대폭 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ScoopBack</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>퍼담아!</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>적의 투사체를 쳐서 되돌림, 맞출시 데미지 150% 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FoilArmor</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>은박갑옷</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5초간 받는 데미지 50% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PoisonChef</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>독요리사</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>타격한 적이 5초간 동료 적을 공격함 (혼란)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FlamePan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>화염팬</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>근접 타격이 화상 부여, 3초간 지속 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Biohazard</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>생화학무기</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>자기 주변 넓은 범위 지속 데미지 장판 8초</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SatelliteDish</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>위성안테나</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10초간 적 전원 위치 표시 + 가장 먼 적에게 자동 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PercussionDog</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>타악기견</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3초간 주변에 리듬 충격파, 박자마다 적 넉백</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SpicyFoilGrill</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>매운은박구이</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>설치형 함정, 밟은 적 즉시 경직 + 방어력 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LockBreaker</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>자물쇠깨기</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>보스 방어막 무시하고 직접 타격 가능 (10초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UltimateStench</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>역대급악취</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>맵 전체 적 이동속도 30% 감소 15초간</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SpicyRain</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>매운비</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>하늘에서 고추냉이 비가 내림, 전체 적 지속 데미지 3초(-10%), 쿨타임 20초</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CateringChef</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>출장요리사</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>랜덤 위치 3곳에 프라이팬 내려찍기, 범위 스턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FoilParcel</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>은박택배</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>적에게 달라붙는 시한폭탄 부착, 3초 후 폭발</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WindLadle</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>바람국자</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>전방에 강한 바람, 적 전원 위쪽으로 밀어내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RedCliffsBattle</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>적벽대전</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>전방 넓은 부채꼴 화염 공격, 적 전원 화상(지속 대미지 -5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SpicyRabbit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>매운토끼</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>당근 유도탄 3발 발사, 맞은 적 경직 + 지속 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UpsetTummyBear</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>배탈곰</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>자폭형 곰인형 소환, 적에게 걸어가서 폭발</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HomeShopping</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>홈쇼핑</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5초간 공격속도 2배</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MirrorLandLadle</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>거울나라의 국자</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>자신의 공격이 전부 2회 반복됨 (8초간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SignalJam</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전파교란</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>적 전원 3초간 랜덤 방향으로 이동 (조작 반전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HellsKitchen</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>지옥의주방</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>맵 전체 10초간 모든 적 지속 데미지 + 혼란</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TerrorDoll</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>테러인형</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>곰인형이 적진 돌진, 범위 기절 + 중독</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ArmyCook</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>군영취사병</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20초간 아군 유닛 3마리 소환</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UfoDog</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UFO견</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>쿠킹호일 UFO 오라, 5초간 적 공격 무시 + 자동 레이저 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SurvivalKit</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>생존키트</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1회 부활 + 부활 시 주변 적 밀어내기 + 3초 무적</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CarrotShield</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>당근방패</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>피격 시 당근 파편이 주변 적에게 반사 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CozyShield</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>포근방패</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>피격 시 30% 확률로 데미지 무효화</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pause</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>일시정지</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>화면 내 적 전체 1.5초 정지 (쿨타임 10초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>StrategistDog</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>지략견</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>적이 서로 가장 가까운 적을 공격함 (동요 5초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CurseDoll</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>저주인형</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>받은 데미지 200%를 가장 가까운 적에게 전달 (8초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ChannelSurf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>채널서핑</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5초마다 랜덤 버프 1개 부여 (20초간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ChannelShuffle</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>채널돌리개</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>적들의 위치를 랜덤으로 섞어버림</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PuppetTroupe</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>인형극단</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>인형 2개가 주변을 돌며 자동 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BearGuanYu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>관곰</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>15초간 공격력 대폭 상승 + 타격 시 적 밀어내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CarrotMissile</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>당근미사일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>리모컨 누르면 유도 당근 5발 연속 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DongtakMirror</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>동탁의거울</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>가장 강한 적 1마리 10초간 아군 전환,</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DollLegion</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>인형군단</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>분신 인형 5개 소환, 각각 자동 공격 10초</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ThreeKingdomsShow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>삼국지극장</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>관우·장비·조조 곰인형 3마리 소환, 15초간 전투</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SweepAway</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>쓸어버려!</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>근접공격, 전방 넓은 범위 밀어내기 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CushionBumper</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>쿠션범퍼</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>적과 충돌 시 자동 넉백 + 충격파 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DustCloud</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>먼지구름</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5초간 회피율 80%, 적 공격이 거의 안 맞음</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WhipDog</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>채찍개</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>사거리 2배 증가, 긴 거리에서 적 타격 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EnergizerDog</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>에너자이개</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10초간 모든 쿨타임 50% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DustStorm</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>먼지폭풍</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>토네이도 소환, 적을 빨아들여 한곳에 모은 뒤 폭발</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ElectricDog</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>전기견</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>공격마다 감전, 감전된 적끼리 가까우면 연쇄 번개</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WitchDog</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>마녀견</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10초간 적 공격 무시 + 위에서 쿠션 투하 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AllergyBomb</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>알레르기폭탄</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>적 전원 재채기, 3초간 공격 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ElectricBroom</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>전기빗자루</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>전방 쓸기 공격에 감전 추가, 감전시 4초간 정지, 데미지 40% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ElectricCushion</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>전기방석</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>터치로 원하는 곳에 설치, 밟은 적 5초간 감전으로 이동불가, 쿨타임 5초, 한 번 밟으면 사라짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UltimateRemote</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>완전체리모컨</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>적 1마리 지정, 가장 가까이에 있는 적에게 돌진하여 동귀어진</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>StaticDog</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>정전기개</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>접촉한 적 전원 3초 마비, 연쇄 감전</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MoldSpore</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>곰팡이포자</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>맵에 곰팡이 지대 생성, 적 지속 데미지 + 둔화</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CarrotPunch</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>당근펀치</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>이동속도 상승 + 당근 인형이 10초에 한 번씩 갈림, 당근 인형을 밟으면 속도 50% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NapSet</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>낮잠세트</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>주변 적 전원 수면 5초, 피격 시 깨어남</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LaserDog</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>레이저견</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>거울에서 레이저 반사, 직선상 적 전원 관통 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ElectricChef</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>전기요리사</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>감전 프라이팬 3연타 + 마지막 타격 범위 폭발</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TrashStorm</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>쓰레기폭풍</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>잡동사니 토네이도, 적 끌어모아 12초간 지속 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ArchmageDog</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>대마법사견</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>10초간 적 공격 무시 + 번개 자동 공격 + 분신 소환</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>StoneHead</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>돌머리</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>방어력 대폭 상승, 이동속도 30% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DandelionFluff</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>민들레솜</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8초간 적 공격 무시 + 홀씨 자동 범위 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TunnelDog</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>땅굴개</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>지하 잠입, 3초 후 지정 위치에서 솟아올라 범위 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WaterGun</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>워터건</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>전방 직선 물줄기, 적 밀어내기 + 3초 둔화</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CrossbowDog</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>석궁견</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>돌멩이를 대나무로 발사, 관통형 원거리 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FlowerRain</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>꽃비</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>홀씨가 맵 전체 흩뿌려짐, 적 전원 시야 차단 5초</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EarthquakeDog</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>지진개</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>땅을 흔들어 맵 전체 적 넘어뜨림 2초</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mudpit</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>진흙탕</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>맵 바닥 진흙 변경, 적 이동속도 50% 감소 10초</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BambooFlute</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>대나무피리</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>아름다운 선율, 적 전원 매혹 5초간 제자리 춤</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WaterCannon</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>물대포</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>대나무 통에 물 압축, 전방 초강력 일직선 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>StoneGrill</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>돌구이</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>달궈진 돌 투척 3발, 맞은 자리에 화상 장판</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ShockHose</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>감전호스</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>물줄기에 전기, 맞은 적 전원 연쇄 감전</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FishingDog</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>낚시개</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>지렁이 미끼로 적 끌어당겨 곰인형이 5초 속박</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IllusionFlower</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>환상의꽃</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>분신 3마리 각각 민들레 홀씨 공격, 넓은 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ZhugeLiangDog</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>제갈량견</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>15초간 적 이동 경로 예측 + 함정 자동 설치</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Catapult</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>투석기</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>쿠션에 돌 올려 발사, 포물선 범위 공격 3연발</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SpoiledFountain</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>상한분수</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>독우유 분수 뿌림, 주변 적 중독 + 둔화</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Outsider</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>아웃사이더</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>너무 역겨워서 적 전원 도망 8초</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FlowerWindSweep</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>꽃바람청소</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>홀씨 토네이도, 적 빨아들인 뒤 큰 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ElectricRod</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>전기봉</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>근접 공격 시 100% 감전 + 범위 확대</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GolemSummon</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>골렘소환</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>돌 골렘 1마리 소환, 20초간 대신 싸워줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TearGas</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>최루가스</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>맵 전체 안개, 적 명중률 0%에 가까움 3초</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PuppetControl</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>인형조종술</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>거대 당근인형 소환, 리모컨으로 직접 조종 12초</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WitchsSoup</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>마녀의수프</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>독 가마솥 설치, 주변 적 흡입 + 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>WallBuild</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>성벽건설</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>맵에 돌벽 3개 생성, 적 부딪히면 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>GardenMaster</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>정원의주인</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>마당 전체 아군 영역, 적 자동 데미지 + 아군 회복 20초</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FadedStar</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>한물간스타</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>적 전원 비웃음, 5초간 방어력 0으로 감소</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,21 @@
           <t>trigger</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cutsceneId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>standing</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2373,11 +2388,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>InspectWall</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2486,11 +2496,6 @@
           <t>ghost1</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>InspectHolyWater</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3726,6 +3731,1115 @@
       <c r="E122" t="inlineStr">
         <is>
           <t>ghost1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tut1_nar_01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>언제나처럼 평화로운 {name}의 하우스.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>tut1_nar_02</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>tut1_nar_02</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>주인님은 사냥 나가고 {name} 혼자 집을 지키게 된지 3시간째.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>tut1_nar_03</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tut1_nar_03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>집에만 있는 다고 노는게 아니다!</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>tut1_nar_04</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>tut1_nar_04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>할 일이 얼마나 많은지 말로는 전부 말할 수가 없다.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>tut1_nar_05</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>tut1_nar_05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>마당부터 방까지 순찰,</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>tut1_nar_06</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>tut1_nar_06</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>대문 앞에서 10분동안 주인님 그리워하기,</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>tut1_nar_07</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>tut1_nar_07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>주방에 먹을게 없나 찬장 열어보기-...</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>tut1_dog_01</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>tut1_dog_01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>잠시만!</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>tut1_dog_02</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>tut1_dog_02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>지금  아주 개인적인 사생활이 폭로되는 기분이었는데?</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>tut1_dog_03</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>tut1_dog_03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>아잇, 오늘 마가 꼈나</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>tut1_dog_04</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>tut1_dog_04</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>주방에 먹은 건 하나도 없고</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>tut1_dog_05</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>tut1_dog_05</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>야채만 잔뜩 있었다구</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>tut1_dog_06</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>tut1_dog_06</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>치커리? 샐러드? 그런걸 인간들은 왜 먹는거야?</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>tut1_dog_07</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>tut1_dog_07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>입맛만 버렸네!</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>tut1_dog_08</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>tut1_dog_08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>오전 루틴은 망쳤지만 오후까진 망칠 순 없지!</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>tut1_dog_09</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>tut1_dog_09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>열심히 주인을 삥뜯어서 산 인형~</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>tut1_dog_10</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>tut1_dog_10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>우리 곰뻥이 어디 갓-</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>tut1_bear_01</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>tut1_bear_01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>tut1_rage_01</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>TutorialBear</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>tut1_rage_01</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>으아아아아아아</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>tut1_rage_02</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>tut1_rage_02</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>으아아아</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>tut1_rage_03</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>tut1_rage_03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>으아아아아아아아악</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>tut1_rage_04</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>tut1_rage_04</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>곰뻥이가 죽었다!</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>tut1_rage_05</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>tut1_rage_05</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>곰뻥이 모가지가 똑떨어지려고 하잖아!</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>tut1_rage_06</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>tut1_rage_06</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>아니 이미 뚝 떨어졌잖아?!</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>tut1_rage_07</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>tut1_rage_07</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>안 돼!</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>tut1_rage_08</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>tut1_rage_08</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>이럴 순 없어!!!!!!!!!!</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>tut1_rage_09</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>tut1_rage_09</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>이럴 순 없,</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>tut1_calm_01</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>tut1_calm_01</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>잠시만</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>tut1_calm_02</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>tut1_calm_02</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>이거 AS되는 인형 아니야?</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>tut1_calm_03</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>tut1_calm_03</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>처음 데려왔을 때 제품설명서 꼼꼼하게 읽을걸</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>tut1_calm_04</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>tut1_calm_04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>tut1_calm_05</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>tut1_calm_05</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>후회해도 어쩔 수 없지...</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>tut1_calm_06</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>tut1_calm_06</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>이렇게 된거 집먼지놈들을 패서 알아내야겠다</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>tut1_99</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>tut1_00</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>tut1_01</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>TutorialSummon</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>tut1_01</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>tut1_02</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>NameInput</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>tut1_02</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>tut1_nar_01</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>TutorialDogLine</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>tut1_99</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>tut1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>TutorialEnemy</t>
         </is>
       </c>
     </row>

--- a/Assets/CSV/GameData.xlsx
+++ b/Assets/CSV/GameData.xlsx
@@ -4854,7 +4854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4988,6 +4988,11 @@
           <t>clearedIntroText</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>clearRequirement</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5065,6 +5070,9 @@
           <t>깔끔하게 클리어!</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5127,6 +5135,9 @@
           <t>적이 조금 늘었다</t>
         </is>
       </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5189,6 +5200,9 @@
           <t>점점 거세진다</t>
         </is>
       </c>
+      <c r="AA4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5251,6 +5265,9 @@
           <t>쉽지 않아</t>
         </is>
       </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5313,6 +5330,9 @@
           <t>거의 다 왔다</t>
         </is>
       </c>
+      <c r="AA6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5375,6 +5395,9 @@
           <t>복도의 끝</t>
         </is>
       </c>
+      <c r="AA7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5442,6 +5465,9 @@
           <t>복도 정복!</t>
         </is>
       </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5503,6 +5529,9 @@
         <is>
           <t>새로운 구역 골목이다</t>
         </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
